--- a/MainTop/10.09.2026 Макс Озон/print.xlsx
+++ b/MainTop/10.09.2026 Макс Озон/print.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\10.09.2026 Макс Озон\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B24E76D-E59E-416C-B2E4-DF64DD2D00E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -247,8 +253,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -281,17 +287,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Стандартная">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -329,9 +343,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Стандартная">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -363,9 +377,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -397,9 +429,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Стандартная">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -572,11 +622,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I68"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -605,7 +655,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -628,10 +678,10 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -657,7 +707,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -683,7 +733,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -709,7 +759,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -735,7 +785,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -761,7 +811,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -787,7 +837,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -813,7 +863,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -839,7 +889,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -865,7 +915,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -891,7 +941,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -917,7 +967,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -943,7 +993,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -969,7 +1019,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -995,7 +1045,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -1021,7 +1071,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -1047,7 +1097,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -1073,7 +1123,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -1099,7 +1149,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -1125,7 +1175,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -1151,7 +1201,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -1177,7 +1227,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -1203,7 +1253,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -1229,7 +1279,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -1255,7 +1305,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>34</v>
       </c>
@@ -1281,7 +1331,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>35</v>
       </c>
@@ -1307,7 +1357,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -1333,7 +1383,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -1359,7 +1409,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>38</v>
       </c>
@@ -1385,7 +1435,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>39</v>
       </c>
@@ -1411,7 +1461,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -1437,7 +1487,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>41</v>
       </c>
@@ -1463,7 +1513,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>42</v>
       </c>
@@ -1489,7 +1539,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>43</v>
       </c>
@@ -1515,7 +1565,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>44</v>
       </c>
@@ -1541,7 +1591,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>45</v>
       </c>
@@ -1567,7 +1617,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>46</v>
       </c>
@@ -1593,7 +1643,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>47</v>
       </c>
@@ -1619,7 +1669,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>48</v>
       </c>
@@ -1645,7 +1695,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>49</v>
       </c>
@@ -1671,7 +1721,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>50</v>
       </c>
@@ -1697,7 +1747,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>51</v>
       </c>
@@ -1723,7 +1773,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>52</v>
       </c>
@@ -1749,7 +1799,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>53</v>
       </c>
@@ -1775,7 +1825,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>54</v>
       </c>
@@ -1801,7 +1851,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>55</v>
       </c>
@@ -1827,7 +1877,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>56</v>
       </c>
@@ -1853,7 +1903,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>57</v>
       </c>
@@ -1879,7 +1929,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>58</v>
       </c>
@@ -1905,7 +1955,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>59</v>
       </c>
@@ -1931,7 +1981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>60</v>
       </c>
@@ -1957,7 +2007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:9">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>61</v>
       </c>
@@ -1983,7 +2033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>62</v>
       </c>
@@ -2009,7 +2059,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>63</v>
       </c>
@@ -2035,7 +2085,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>64</v>
       </c>
@@ -2061,7 +2111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>65</v>
       </c>
@@ -2087,7 +2137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>66</v>
       </c>
@@ -2113,7 +2163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>67</v>
       </c>
@@ -2139,7 +2189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:9">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>68</v>
       </c>
@@ -2165,7 +2215,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:9">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>69</v>
       </c>
@@ -2191,7 +2241,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:9">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>70</v>
       </c>
@@ -2217,7 +2267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:9">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>71</v>
       </c>
@@ -2243,7 +2293,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:9">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>72</v>
       </c>
@@ -2269,7 +2319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:9">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>73</v>
       </c>
@@ -2295,7 +2345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:9">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>74</v>
       </c>
@@ -2321,7 +2371,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:9">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>75</v>
       </c>
